--- a/artfynd/A 12215-2025 artfynd.xlsx
+++ b/artfynd/A 12215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4625792</v>
+        <v>5041529</v>
       </c>
       <c r="B2" t="n">
-        <v>96952</v>
+        <v>98519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222309</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -789,127 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5041529</v>
-      </c>
-      <c r="B3" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ängsrest vid SLÅTTERTORPEN, Vg</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>450886.4842810578</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6528801.304272464</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Gullspång</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Hova</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1994-05-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1994-05-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rapporterad av Arne Sjögren</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
         </is>
